--- a/c_sickness.xlsx
+++ b/c_sickness.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/paigecole/Documents/VT M.A. History/hist5444s26/celestia_world_test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF2B6C1C-6A70-1A4C-880E-2C9C7C282E1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{4E478A65-8DC3-FA4B-A244-72A71F5898EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="600" windowWidth="28040" windowHeight="16660" xr2:uid="{0C5A5809-3A33-9949-9A07-E35AF94930FF}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="100">
   <si>
     <t>month</t>
   </si>
@@ -317,6 +317,9 @@
   </si>
   <si>
     <t>I have a hard cold and am trying to get rid of it</t>
+  </si>
+  <si>
+    <t>times mentioned</t>
   </si>
 </sst>
 </file>
@@ -1177,618 +1180,678 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEEC4D56-3A05-B84A-AD8C-94901B919B8E}">
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
       <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
       <c r="D3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
         <v>13</v>
       </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
       <c r="D4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" t="s">
         <v>14</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
         <v>17</v>
       </c>
-      <c r="C5" t="s">
-        <v>7</v>
-      </c>
       <c r="D5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" t="s">
         <v>8</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
         <v>19</v>
       </c>
-      <c r="C6" t="s">
-        <v>7</v>
-      </c>
       <c r="D6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" t="s">
         <v>8</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>21</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
         <v>22</v>
       </c>
-      <c r="C7" t="s">
-        <v>7</v>
-      </c>
       <c r="D7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" t="s">
         <v>11</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>24</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
         <v>25</v>
       </c>
-      <c r="C8" t="s">
-        <v>7</v>
-      </c>
       <c r="D8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" t="s">
         <v>26</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>28</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
         <v>29</v>
       </c>
-      <c r="C9" t="s">
-        <v>7</v>
-      </c>
       <c r="D9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" t="s">
         <v>30</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>28</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
         <v>32</v>
       </c>
-      <c r="C10" t="s">
-        <v>7</v>
-      </c>
       <c r="D10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" t="s">
         <v>8</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>28</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
         <v>34</v>
       </c>
-      <c r="C11" t="s">
-        <v>7</v>
-      </c>
       <c r="D11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" t="s">
         <v>35</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>28</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
         <v>37</v>
       </c>
-      <c r="C12" t="s">
-        <v>7</v>
-      </c>
       <c r="D12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" t="s">
         <v>35</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>39</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
         <v>40</v>
       </c>
-      <c r="C13" t="s">
-        <v>7</v>
-      </c>
       <c r="D13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" t="s">
         <v>11</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>42</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14">
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
         <v>43</v>
       </c>
-      <c r="C14" t="s">
-        <v>7</v>
-      </c>
       <c r="D14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" t="s">
         <v>44</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>42</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
         <v>46</v>
       </c>
-      <c r="C15" t="s">
-        <v>7</v>
-      </c>
       <c r="D15" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" t="s">
         <v>47</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>49</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16">
+        <v>15</v>
+      </c>
+      <c r="C16" t="s">
         <v>50</v>
       </c>
-      <c r="C16" t="s">
-        <v>7</v>
-      </c>
       <c r="D16" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" t="s">
         <v>11</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>52</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17">
+        <v>16</v>
+      </c>
+      <c r="C17" t="s">
         <v>53</v>
       </c>
-      <c r="C17" t="s">
-        <v>7</v>
-      </c>
       <c r="D17" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" t="s">
         <v>11</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>52</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
         <v>55</v>
       </c>
-      <c r="C18" t="s">
-        <v>7</v>
-      </c>
       <c r="D18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" t="s">
         <v>8</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>57</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19">
+        <v>18</v>
+      </c>
+      <c r="C19" t="s">
         <v>58</v>
       </c>
-      <c r="C19" t="s">
-        <v>7</v>
-      </c>
       <c r="D19" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" t="s">
         <v>59</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>61</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20">
+        <v>19</v>
+      </c>
+      <c r="C20" t="s">
         <v>62</v>
       </c>
-      <c r="C20" t="s">
-        <v>7</v>
-      </c>
       <c r="D20" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" t="s">
         <v>63</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>61</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>65</v>
       </c>
-      <c r="C21" t="s">
-        <v>7</v>
-      </c>
       <c r="D21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" t="s">
         <v>8</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>61</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>67</v>
       </c>
-      <c r="C22" t="s">
-        <v>7</v>
-      </c>
       <c r="D22" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" t="s">
         <v>30</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>61</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>69</v>
       </c>
-      <c r="C23" t="s">
-        <v>7</v>
-      </c>
       <c r="D23" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" t="s">
         <v>30</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>61</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>65</v>
       </c>
-      <c r="C24" t="s">
-        <v>7</v>
-      </c>
       <c r="D24" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" t="s">
         <v>30</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>61</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>72</v>
       </c>
-      <c r="C25" t="s">
-        <v>7</v>
-      </c>
       <c r="D25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" t="s">
         <v>30</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>61</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>74</v>
       </c>
-      <c r="C26" t="s">
-        <v>7</v>
-      </c>
       <c r="D26" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" t="s">
         <v>30</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>61</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>76</v>
       </c>
-      <c r="C27" t="s">
-        <v>7</v>
-      </c>
       <c r="D27" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27" t="s">
         <v>77</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>61</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>79</v>
       </c>
-      <c r="C28" t="s">
-        <v>7</v>
-      </c>
       <c r="D28" t="s">
+        <v>7</v>
+      </c>
+      <c r="E28" t="s">
         <v>77</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>81</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>82</v>
       </c>
-      <c r="C29" t="s">
-        <v>7</v>
-      </c>
       <c r="D29" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" t="s">
         <v>77</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>81</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>84</v>
       </c>
-      <c r="C30" t="s">
-        <v>7</v>
-      </c>
       <c r="D30" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30" t="s">
         <v>30</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>81</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>86</v>
       </c>
-      <c r="C31" t="s">
-        <v>7</v>
-      </c>
       <c r="D31" t="s">
+        <v>7</v>
+      </c>
+      <c r="E31" t="s">
         <v>30</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>81</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>88</v>
       </c>
-      <c r="C32" t="s">
-        <v>7</v>
-      </c>
       <c r="D32" t="s">
+        <v>7</v>
+      </c>
+      <c r="E32" t="s">
         <v>89</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>81</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>91</v>
       </c>
-      <c r="C33" t="s">
-        <v>7</v>
-      </c>
       <c r="D33" t="s">
+        <v>7</v>
+      </c>
+      <c r="E33" t="s">
         <v>89</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>81</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>93</v>
       </c>
-      <c r="C34" t="s">
-        <v>7</v>
-      </c>
       <c r="D34" t="s">
+        <v>7</v>
+      </c>
+      <c r="E34" t="s">
         <v>89</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>81</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>95</v>
       </c>
-      <c r="C35" t="s">
-        <v>7</v>
-      </c>
       <c r="D35" t="s">
+        <v>7</v>
+      </c>
+      <c r="E35" t="s">
         <v>89</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>81</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>97</v>
       </c>
-      <c r="C36" t="s">
-        <v>7</v>
-      </c>
       <c r="D36" t="s">
+        <v>7</v>
+      </c>
+      <c r="E36" t="s">
         <v>89</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>98</v>
       </c>
     </row>
